--- a/Employee_Reports_wi48/Sugathadasa Pattiwilage Q0376.xlsx
+++ b/Employee_Reports_wi48/Sugathadasa Pattiwilage Q0376.xlsx
@@ -463,13 +463,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="73" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-479</v>
+        <v>-482</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1619,9 +1619,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
           <t>06-Jun-2026</t>
@@ -1633,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1682,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1719,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1768,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1817,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1854,11 +1866,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1869,41 +1881,90 @@
       <c r="K30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Matar LOTO Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>MATAR</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>FM-DE-24-SOP-SA-013</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>01-Jul-2026</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>01-Jul-2027</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>20-Aug-2024</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>20-Aug-2026</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="H32" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2057,7 +2118,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2080,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2152,7 +2213,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2181,7 +2242,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2210,7 +2271,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2239,7 +2300,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2268,7 +2329,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2297,7 +2358,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2326,7 +2387,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2355,7 +2416,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2384,7 +2445,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2392,6 +2453,151 @@
         </is>
       </c>
       <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>uldtv 20ft</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>uldtv 15ft</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>bbtv 20ft</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>bbtv 15ft</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
